--- a/Results/Exam_Output_5.xlsx
+++ b/Results/Exam_Output_5.xlsx
@@ -1,25 +1,187 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cebajel/Documents/Education/Great/Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD893C02-EDB9-1A47-BDFB-9C45F369B9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="University Timetable" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Slot 1</t>
+  </si>
+  <si>
+    <t>Slot 2</t>
+  </si>
+  <si>
+    <t>Mon</t>
+  </si>
+  <si>
+    <t>BB 810
+CE 202
+CS 607
+EE 221
+EE 227
+EE 321
+EE 601
+EE 607
+HS 103
+ME 324
+ME 608
+PH 103</t>
+  </si>
+  <si>
+    <t>CE 201
+CS 303
+CS 810
+EE 622
+ME 207
+ME 903</t>
+  </si>
+  <si>
+    <t>Tue</t>
+  </si>
+  <si>
+    <t>BB 301
+CE 601
+CS 213
+CS 609
+EE 205
+EE 631
+EE 688
+HS 106
+ME 212
+ME 222
+ME 421
+ME 605
+PH 201
+PH 302</t>
+  </si>
+  <si>
+    <t>CS 101
+CS 403
+EE 629
+MA 321
+ME 643</t>
+  </si>
+  <si>
+    <t>Wed</t>
+  </si>
+  <si>
+    <t>CE 602
+CH 102
+CL 204
+CS 301
+EE 210
+EE 420
+EE 689
+EE 691
+ME 220
+ME 630</t>
+  </si>
+  <si>
+    <t>EE 610
+HS 201
+ME 607
+PH 402</t>
+  </si>
+  <si>
+    <t>Thu</t>
+  </si>
+  <si>
+    <t>BB 103
+CL 802
+CS 203
+CS 601
+EE 621
+MA 201
+MA 203
+MA 209
+ME 203
+ME 305
+ME 446
+ME 609</t>
+  </si>
+  <si>
+    <t>CS 621
+EE 325
+EE 690
+ME 201
+ME 311
+PH 101
+PH 425</t>
+  </si>
+  <si>
+    <t>Fri</t>
+  </si>
+  <si>
+    <t>CE 203
+CH 202
+CH 204
+CL 201
+CS 205
+EE 202
+EE 229
+EE 634
+HS 433
+ME 204
+ME 621
+PH 304</t>
+  </si>
+  <si>
+    <t>HS 409
+HS 425
+HS 501
+MA 101
+ME 309</t>
+  </si>
+</sst>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -27,85 +189,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -390,4 +511,80 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>